--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5528,6 +5528,456 @@
       <c r="H182" t="inlineStr">
         <is>
           <t>Wed Japanese curry</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Pork shoulder (pork butt)</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G183" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Mon pulled pork</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>BBQ sauce</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G184" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Mon pulled pork</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Liquid smoke</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G185" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Mon pulled pork</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Burger buns</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G186" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Mon pulled pork burger</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Sourdough bread</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Fri grilled cheese</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Fontina cheese</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Fridge - Dairy &amp; Eggs</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G188" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Fri grilled cheese</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Gouda cheese</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Fridge - Dairy &amp; Eggs</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G189" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Fri grilled cheese</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Dancing Chef Indonesian Curry Paste</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G190" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Wed Padang curry</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Frozen prata</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G191" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Wed prata</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Luncheon meat</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G192" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Tue luncheon meat &amp; potatoes</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Penne pasta</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G193" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sun arrabbiata</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Firm tofu (tau kwa)</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G194" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>Tue tau yu bak</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Star anise</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G195" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>Tue tau yu bak</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Cinnamon stick</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G196" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Tue tau yu bak</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Whole cloves</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G197" s="7" t="n">
+        <v>46207</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>Tue tau yu bak</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -515,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H197"/>
+  <dimension ref="A1:H206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5978,6 +5978,249 @@
       <c r="H197" t="inlineStr">
         <is>
           <t>Tue tau yu bak</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Mee siam paste</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G198" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>Thu dry mee siam</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="G199" s="7" t="n"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Laksa leaves</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G200" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Mon dry laksa</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Cornmeal</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G201" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>Fri cornbread</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Baby back ribs (pork)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G202" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Fri baby back ribs</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Bread (baguette/roti)</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G203" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Thu with curry</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Dancing Chef laksa paste</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G204" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Mon dry laksa</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Winter melon</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G205" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Mon winter melon soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Baby bok choy</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G206" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Thu side</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -112,6 +112,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H206"/>
+  <dimension ref="A1:H243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -583,7 +586,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -593,8 +596,14 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
+      <c r="G2" s="8" t="n">
+        <v>46228</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Finishing — restock</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -639,7 +648,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -649,8 +658,14 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
+      <c r="G4" s="8" t="n">
+        <v>46228</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Finishing — restock</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1027,7 +1042,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1037,8 +1052,14 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr"/>
+      <c r="G18" s="8" t="n">
+        <v>46228</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Cooking oil — restock</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1689,7 +1710,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1699,8 +1720,14 @@
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr"/>
+      <c r="G43" s="8" t="n">
+        <v>46228</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>1 pack left</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -6221,6 +6248,1111 @@
       <c r="H206" t="inlineStr">
         <is>
           <t>Thu side</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Udon noodles</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G207" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>Mon udon</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Kombu (kelp)</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G208" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>Mon udon broth</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Steamed buns (gua bao/mantou)</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G209" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Thu kong bak pau</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Black fungus (wood ear)</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G210" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>Thu hot &amp; sour soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Sichuan peppercorns</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G211" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Thu hot &amp; sour soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Kabocha / pumpkin</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G212" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Mon yasai tempura</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Youtiao</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G213" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Wed congee</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Old cucumber</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G214" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Fri soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Japanese leek (naganegi)</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G215" s="7" t="n">
+        <v>46214</v>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Tue chicken tsukune</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Dish sponge</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Household / Cleaning</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="G216" s="7" t="n">
+        <v>46228</v>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>For plates</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Steel wool sponge (scourer)</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Household / Cleaning</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Kitchen</t>
+        </is>
+      </c>
+      <c r="G217" s="7" t="n">
+        <v>46228</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Lotus root</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G218" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Tue lotus root pork rib soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Yam / taro (芋头)</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G219" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Fri yam rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Chinese chives (ku chai)</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G220" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Wed ee-fu mee</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Long beans</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G221" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Wed Thai fish cakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Lemongrass</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G222" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Thu chicken rendang</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Galangal</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G223" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Thu chicken rendang</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Kaffir lime leaves</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G224" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Tue fish, Thu rendang, Wed fish cakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Thai basil</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G225" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Wed Thai fish cakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Red spur chilli (large mild)</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G226" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Wed fish cake dipping sauce</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Celery</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G227" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Wed chicken &amp; vegetable soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Fresh thyme</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G228" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Wed chicken &amp; vegetable soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Fresh parsley</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G229" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Wed chicken &amp; vegetable soup</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Sea bass (whole)</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G230" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Tue Thai style steamed fish</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Basa fillets</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G231" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Wed Thai fish cakes (tod mun pla)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Cardamom pods</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G232" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Thu chicken rendang</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Coriander powder</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G233" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Thu chicken rendang</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>Baking powder</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G234" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Tue sticky honey pork - NOT interchangeable with baking soda</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>Tamarind paste</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G235" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Thu chicken rendang</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Grated coconut</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G236" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Thu rendang - kerisik</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Glutinous rice</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G237" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Lotus leaf rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Lotus leaf (dried)</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G238" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Lotus leaf rice</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Whole duck</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G239" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Teochew braised duck (~2kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Mei cai (preserved mustard greens)</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G240" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Mei cai kou rou - soak &amp; rinse well before use</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Dried bamboo shoots (笋干)</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G241" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Winter melon bamboo shoot ham soup - NOT the canned bamboo shoots; soak overnight</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Madam Kwan's rendang paste</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G242" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Thu beef rendang - buy 2 packets; FairPrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Beef chuck / stewing beef (sliced)</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G243" s="7" t="n">
+        <v>46235</v>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Thu beef rendang - 900g-1kg sliced</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H243"/>
+  <dimension ref="A1:H248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7353,6 +7353,156 @@
       <c r="H243" t="inlineStr">
         <is>
           <t>Thu beef rendang - 900g-1kg sliced</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Instant cereal (Nestum)</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G244" s="7" t="n">
+        <v>46242</v>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Cereal pork chop</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Curry leaves</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G245" s="7" t="n">
+        <v>46242</v>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Cereal pork chop</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Hoisin sauce</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G246" s="7" t="n">
+        <v>46242</v>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Braised pork ribs</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Holy basil (kaprow)</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G247" s="7" t="n">
+        <v>46242</v>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Pork krapow - Thai basil substitutes</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Prime pork ribs</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G248" s="7" t="n">
+        <v>46242</v>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Braised pork ribs</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -518,7 +518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H248"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -7503,6 +7503,36 @@
       <c r="H248" t="inlineStr">
         <is>
           <t>Braised pork ribs</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Satay (frozen)</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>In stock</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G249" s="7" t="n">
+        <v>46243</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Fri - using up existing stock</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -20,8 +20,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -97,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +116,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H249"/>
+  <dimension ref="A1:H268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -586,7 +591,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -596,8 +601,8 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="8" t="n">
-        <v>46228</v>
+      <c r="G2" s="9" t="n">
+        <v>46271</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -618,7 +623,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr"/>
@@ -628,7 +633,9 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>For braising / dark colour</t>
@@ -648,7 +655,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr"/>
@@ -658,8 +665,8 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="8" t="n">
-        <v>46228</v>
+      <c r="G4" s="9" t="n">
+        <v>46271</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -680,7 +687,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr"/>
@@ -690,7 +697,9 @@
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -706,7 +715,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
@@ -716,7 +725,9 @@
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -732,7 +743,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
@@ -742,7 +753,9 @@
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Pork rib king gravy</t>
@@ -762,7 +775,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr"/>
@@ -772,7 +785,9 @@
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Pork rib king gravy</t>
@@ -792,7 +807,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr"/>
@@ -802,7 +817,9 @@
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Pork rib king gravy</t>
@@ -822,7 +839,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr"/>
@@ -832,7 +849,9 @@
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
@@ -848,7 +867,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr"/>
@@ -858,7 +877,9 @@
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
@@ -874,7 +895,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr"/>
@@ -884,7 +905,9 @@
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Eggplant w/ minced pork</t>
@@ -904,7 +927,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
@@ -914,7 +937,9 @@
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
@@ -930,7 +955,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -940,7 +965,9 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>For mayo</t>
@@ -960,7 +987,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
@@ -970,7 +997,9 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr"/>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
           <t>For mayo</t>
@@ -990,7 +1019,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1000,7 +1029,9 @@
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1016,7 +1047,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -1026,7 +1057,9 @@
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr"/>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
@@ -1042,7 +1075,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1052,8 +1085,8 @@
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr"/>
-      <c r="G18" s="8" t="n">
-        <v>46228</v>
+      <c r="G18" s="9" t="n">
+        <v>46271</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
@@ -1074,7 +1107,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
@@ -1084,7 +1117,9 @@
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr"/>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>For wasabi mayo prawns</t>
@@ -1104,7 +1139,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
@@ -1114,7 +1149,9 @@
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
@@ -1130,7 +1167,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -1140,7 +1177,9 @@
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
@@ -1156,7 +1195,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1166,7 +1205,9 @@
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr"/>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
@@ -1182,7 +1223,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1192,7 +1233,9 @@
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr"/>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Optional - orange mayo</t>
@@ -1212,7 +1255,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -1222,7 +1265,9 @@
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -1238,7 +1283,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1248,7 +1293,9 @@
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
@@ -1264,7 +1311,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
@@ -1274,7 +1321,9 @@
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr"/>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
@@ -1290,7 +1339,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
@@ -1300,7 +1349,9 @@
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr"/>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
@@ -1316,7 +1367,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
@@ -1326,7 +1377,9 @@
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr"/>
-      <c r="G28" s="2" t="inlineStr"/>
+      <c r="G28" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
@@ -1342,7 +1395,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
@@ -1352,7 +1405,9 @@
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr"/>
-      <c r="G29" s="2" t="inlineStr"/>
+      <c r="G29" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
@@ -1368,7 +1423,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1378,7 +1433,9 @@
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
+      <c r="G30" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1394,7 +1451,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
@@ -1404,7 +1461,9 @@
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr"/>
-      <c r="G31" s="2" t="inlineStr"/>
+      <c r="G31" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
@@ -1420,7 +1479,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
@@ -1430,7 +1489,9 @@
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr"/>
-      <c r="G32" s="2" t="inlineStr"/>
+      <c r="G32" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
@@ -1446,7 +1507,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
@@ -1456,7 +1517,9 @@
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr"/>
-      <c r="G33" s="2" t="inlineStr"/>
+      <c r="G33" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Meat tenderiser</t>
@@ -1476,7 +1539,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
@@ -1486,7 +1549,9 @@
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr"/>
-      <c r="G34" s="2" t="inlineStr"/>
+      <c r="G34" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
@@ -1502,7 +1567,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -1512,7 +1577,9 @@
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr"/>
-      <c r="G35" s="2" t="inlineStr"/>
+      <c r="G35" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
@@ -1528,7 +1595,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -1538,7 +1605,9 @@
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr"/>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
@@ -1554,7 +1623,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
@@ -1564,7 +1633,9 @@
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
@@ -1580,7 +1651,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
@@ -1590,7 +1661,9 @@
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
@@ -1606,7 +1679,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
@@ -1616,7 +1689,9 @@
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
@@ -1632,7 +1707,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -1642,7 +1717,9 @@
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr"/>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
@@ -1658,7 +1735,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
@@ -1668,7 +1745,9 @@
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr"/>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
@@ -1684,7 +1763,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
@@ -1694,7 +1773,9 @@
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr"/>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
@@ -1710,7 +1791,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
@@ -1720,8 +1801,8 @@
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr"/>
-      <c r="G43" s="8" t="n">
-        <v>46228</v>
+      <c r="G43" s="9" t="n">
+        <v>46271</v>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
@@ -1742,7 +1823,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1752,7 +1833,9 @@
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr"/>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
@@ -1768,7 +1851,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1778,7 +1861,9 @@
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr"/>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
@@ -1794,7 +1879,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
@@ -1804,7 +1889,9 @@
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr"/>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1820,7 +1907,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
@@ -1830,7 +1917,9 @@
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr"/>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
@@ -1846,7 +1935,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -1856,7 +1945,9 @@
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
@@ -1872,7 +1963,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
@@ -1882,7 +1973,9 @@
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr"/>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
@@ -1898,7 +1991,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
@@ -1908,7 +2001,9 @@
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr"/>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Soup ingredient</t>
@@ -1928,7 +2023,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
@@ -1938,7 +2033,9 @@
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr"/>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Optional, soups</t>
@@ -1958,7 +2055,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
@@ -1968,7 +2065,9 @@
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr"/>
-      <c r="G52" s="2" t="inlineStr"/>
+      <c r="G52" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
@@ -1984,7 +2083,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
@@ -1994,7 +2093,9 @@
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr"/>
-      <c r="G53" s="2" t="inlineStr"/>
+      <c r="G53" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Pineapple rice</t>
@@ -2014,7 +2115,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
@@ -2024,7 +2125,9 @@
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr"/>
-      <c r="G54" s="2" t="inlineStr"/>
+      <c r="G54" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
@@ -2050,7 +2153,9 @@
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr"/>
-      <c r="G55" s="2" t="inlineStr"/>
+      <c r="G55" s="9" t="n">
+        <v>46277</v>
+      </c>
       <c r="H55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
@@ -2066,7 +2171,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
@@ -2076,7 +2181,9 @@
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+      <c r="G56" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
@@ -2092,7 +2199,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
@@ -2102,7 +2209,9 @@
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr"/>
-      <c r="G57" s="2" t="inlineStr"/>
+      <c r="G57" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
@@ -2118,7 +2227,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
@@ -2128,7 +2237,9 @@
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr"/>
-      <c r="G58" s="2" t="inlineStr"/>
+      <c r="G58" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
@@ -2144,7 +2255,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
@@ -2154,7 +2265,9 @@
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
+      <c r="G59" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Moroccan stew</t>
@@ -2174,7 +2287,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
@@ -2184,7 +2297,9 @@
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr"/>
+      <c r="G60" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
@@ -2200,7 +2315,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
@@ -2210,7 +2325,9 @@
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
+      <c r="G61" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
@@ -2226,7 +2343,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
@@ -2236,7 +2353,9 @@
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr"/>
-      <c r="G62" s="2" t="inlineStr"/>
+      <c r="G62" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
@@ -2252,7 +2371,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
@@ -2262,7 +2381,9 @@
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr"/>
-      <c r="G63" s="2" t="inlineStr"/>
+      <c r="G63" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
@@ -2278,7 +2399,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
@@ -2288,7 +2409,9 @@
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr"/>
-      <c r="G64" s="2" t="inlineStr"/>
+      <c r="G64" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
@@ -2304,7 +2427,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
@@ -2314,7 +2437,9 @@
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr"/>
-      <c r="G65" s="2" t="inlineStr"/>
+      <c r="G65" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
@@ -2330,7 +2455,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
@@ -2340,7 +2465,9 @@
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr"/>
-      <c r="G66" s="2" t="inlineStr"/>
+      <c r="G66" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
@@ -2356,7 +2483,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
@@ -2366,7 +2493,9 @@
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
+      <c r="G67" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
@@ -2382,7 +2511,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
@@ -2392,7 +2521,9 @@
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr"/>
-      <c r="G68" s="2" t="inlineStr"/>
+      <c r="G68" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
@@ -2408,7 +2539,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
@@ -2418,7 +2549,9 @@
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr"/>
-      <c r="G69" s="2" t="inlineStr"/>
+      <c r="G69" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
@@ -2434,7 +2567,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
@@ -2444,7 +2577,9 @@
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr"/>
-      <c r="G70" s="2" t="inlineStr"/>
+      <c r="G70" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
@@ -2460,7 +2595,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
@@ -2470,7 +2605,9 @@
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr"/>
-      <c r="G71" s="2" t="inlineStr"/>
+      <c r="G71" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
@@ -2486,7 +2623,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
@@ -2496,7 +2633,9 @@
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr"/>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
@@ -2512,7 +2651,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
@@ -2522,7 +2661,9 @@
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr"/>
-      <c r="G73" s="2" t="inlineStr"/>
+      <c r="G73" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
@@ -2538,7 +2679,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
@@ -2548,7 +2689,9 @@
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr"/>
-      <c r="G74" s="2" t="inlineStr"/>
+      <c r="G74" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
@@ -2564,7 +2707,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
@@ -2574,7 +2717,9 @@
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr"/>
-      <c r="G75" s="2" t="inlineStr"/>
+      <c r="G75" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
@@ -2590,7 +2735,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
@@ -2600,7 +2745,9 @@
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr"/>
-      <c r="G76" s="2" t="inlineStr"/>
+      <c r="G76" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
@@ -2616,7 +2763,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
@@ -2626,7 +2773,9 @@
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr"/>
-      <c r="G77" s="2" t="inlineStr"/>
+      <c r="G77" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H77" s="2" t="inlineStr"/>
     </row>
     <row r="78">
@@ -2642,7 +2791,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
@@ -2652,7 +2801,9 @@
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr"/>
-      <c r="G78" s="2" t="inlineStr"/>
+      <c r="G78" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H78" s="2" t="inlineStr"/>
     </row>
     <row r="79">
@@ -2668,7 +2819,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
@@ -2678,7 +2829,9 @@
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr"/>
-      <c r="G79" s="2" t="inlineStr"/>
+      <c r="G79" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H79" s="2" t="inlineStr"/>
     </row>
     <row r="80">
@@ -2694,7 +2847,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
@@ -2704,7 +2857,9 @@
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr"/>
-      <c r="G80" s="2" t="inlineStr"/>
+      <c r="G80" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
@@ -2720,7 +2875,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
@@ -2730,7 +2885,9 @@
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr"/>
-      <c r="G81" s="2" t="inlineStr"/>
+      <c r="G81" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
@@ -2746,7 +2903,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
@@ -2756,7 +2913,9 @@
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr"/>
-      <c r="G82" s="2" t="inlineStr"/>
+      <c r="G82" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
@@ -2772,7 +2931,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
@@ -2782,7 +2941,9 @@
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr"/>
-      <c r="G83" s="2" t="inlineStr"/>
+      <c r="G83" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
@@ -2808,7 +2969,9 @@
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr"/>
-      <c r="G84" s="2" t="inlineStr"/>
+      <c r="G84" s="9" t="n">
+        <v>46277</v>
+      </c>
       <c r="H84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
@@ -2824,7 +2987,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
@@ -2834,7 +2997,9 @@
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
+      <c r="G85" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
@@ -2850,7 +3015,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
@@ -2860,7 +3025,9 @@
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr"/>
-      <c r="G86" s="2" t="inlineStr"/>
+      <c r="G86" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H86" s="2" t="inlineStr"/>
     </row>
     <row r="87">
@@ -2876,7 +3043,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
@@ -2886,7 +3053,9 @@
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="G87" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H87" s="2" t="inlineStr"/>
     </row>
     <row r="88">
@@ -2902,7 +3071,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
@@ -2912,7 +3081,9 @@
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr"/>
-      <c r="G88" s="2" t="inlineStr"/>
+      <c r="G88" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
@@ -2928,7 +3099,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
@@ -2938,7 +3109,9 @@
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="G89" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
@@ -2954,7 +3127,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
@@ -2964,7 +3137,9 @@
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
+      <c r="G90" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H90" s="2" t="inlineStr"/>
     </row>
     <row r="91">
@@ -2980,7 +3155,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
@@ -2990,7 +3165,9 @@
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr"/>
-      <c r="G91" s="2" t="inlineStr"/>
+      <c r="G91" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H91" s="2" t="inlineStr"/>
     </row>
     <row r="92">
@@ -3006,7 +3183,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
@@ -3016,7 +3193,9 @@
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
+      <c r="G92" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H92" s="2" t="inlineStr"/>
     </row>
     <row r="93">
@@ -3032,7 +3211,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
@@ -3042,7 +3221,9 @@
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
+      <c r="G93" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H93" s="2" t="inlineStr"/>
     </row>
     <row r="94">
@@ -3058,7 +3239,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
@@ -3068,7 +3249,9 @@
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr"/>
-      <c r="G94" s="2" t="inlineStr"/>
+      <c r="G94" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H94" s="2" t="inlineStr"/>
     </row>
     <row r="95">
@@ -3084,7 +3267,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
@@ -3094,7 +3277,9 @@
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr"/>
-      <c r="G95" s="2" t="inlineStr"/>
+      <c r="G95" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
@@ -3110,7 +3295,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
@@ -3120,7 +3305,9 @@
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr"/>
-      <c r="G96" s="2" t="inlineStr"/>
+      <c r="G96" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
@@ -3136,7 +3323,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
@@ -3146,7 +3333,9 @@
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr"/>
-      <c r="G97" s="2" t="inlineStr"/>
+      <c r="G97" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
@@ -3162,7 +3351,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
@@ -3172,7 +3361,9 @@
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr"/>
-      <c r="G98" s="2" t="inlineStr"/>
+      <c r="G98" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
@@ -3188,7 +3379,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
@@ -3198,7 +3389,9 @@
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr"/>
-      <c r="G99" s="2" t="inlineStr"/>
+      <c r="G99" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
@@ -3214,7 +3407,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
@@ -3224,7 +3417,9 @@
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr"/>
-      <c r="G100" s="2" t="inlineStr"/>
+      <c r="G100" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
@@ -3240,7 +3435,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
@@ -3250,7 +3445,9 @@
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr"/>
-      <c r="G101" s="2" t="inlineStr"/>
+      <c r="G101" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
@@ -3266,7 +3463,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
@@ -3276,7 +3473,9 @@
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr"/>
-      <c r="G102" s="2" t="inlineStr"/>
+      <c r="G102" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
@@ -3292,7 +3491,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
@@ -3302,7 +3501,9 @@
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr"/>
-      <c r="G103" s="2" t="inlineStr"/>
+      <c r="G103" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
@@ -3318,7 +3519,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
@@ -3328,7 +3529,9 @@
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr"/>
-      <c r="G104" s="2" t="inlineStr"/>
+      <c r="G104" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
@@ -3344,7 +3547,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
@@ -3354,7 +3557,9 @@
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr"/>
-      <c r="G105" s="2" t="inlineStr"/>
+      <c r="G105" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
@@ -3370,7 +3575,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
@@ -3380,7 +3585,9 @@
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr"/>
-      <c r="G106" s="2" t="inlineStr"/>
+      <c r="G106" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
@@ -3396,7 +3603,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
@@ -3406,7 +3613,9 @@
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr"/>
-      <c r="G107" s="2" t="inlineStr"/>
+      <c r="G107" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
@@ -3422,7 +3631,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
@@ -3432,7 +3641,9 @@
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr"/>
-      <c r="G108" s="2" t="inlineStr"/>
+      <c r="G108" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
@@ -3448,7 +3659,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
@@ -3458,7 +3669,9 @@
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr"/>
-      <c r="G109" s="2" t="inlineStr"/>
+      <c r="G109" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
@@ -3474,7 +3687,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
@@ -3484,7 +3697,9 @@
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr"/>
-      <c r="G110" s="2" t="inlineStr"/>
+      <c r="G110" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
@@ -3500,7 +3715,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
@@ -3510,7 +3725,9 @@
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr"/>
-      <c r="G111" s="2" t="inlineStr"/>
+      <c r="G111" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
@@ -3526,7 +3743,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
@@ -3536,7 +3753,9 @@
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
@@ -3552,7 +3771,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
@@ -3562,7 +3781,9 @@
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
@@ -3578,7 +3799,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
@@ -3588,7 +3809,9 @@
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr"/>
-      <c r="G114" s="2" t="inlineStr"/>
+      <c r="G114" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
@@ -3604,7 +3827,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Out</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
@@ -3614,7 +3837,9 @@
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr"/>
+      <c r="G115" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
@@ -3630,7 +3855,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Out</t>
+          <t>In stock</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
@@ -3640,7 +3865,9 @@
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr"/>
+      <c r="G116" s="9" t="n">
+        <v>46277</v>
+      </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Kabayaki / tamagoyaki</t>
@@ -3670,7 +3897,9 @@
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr"/>
-      <c r="G117" s="2" t="inlineStr"/>
+      <c r="G117" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Sweet &amp; sour pork gravy</t>
@@ -3700,7 +3929,9 @@
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr"/>
-      <c r="G118" s="2" t="inlineStr"/>
+      <c r="G118" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Japanese curry</t>
@@ -3730,7 +3961,9 @@
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr"/>
-      <c r="G119" s="2" t="inlineStr"/>
+      <c r="G119" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
           <t>2-3 cans for Wed</t>
@@ -3760,7 +3993,9 @@
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr"/>
-      <c r="G120" s="2" t="inlineStr"/>
+      <c r="G120" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Different from tomato paste; for Japanese curry</t>
@@ -3790,7 +4025,9 @@
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr"/>
-      <c r="G121" s="2" t="inlineStr"/>
+      <c r="G121" s="9" t="n">
+        <v>46271</v>
+      </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Packaged; Sun dinner</t>
@@ -3818,6 +4055,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G122" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H122" t="inlineStr">
         <is>
           <t>Korean fried chicken honey soy sauce</t>
@@ -3845,6 +4085,9 @@
           <t>Spice rack</t>
         </is>
       </c>
+      <c r="G123" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H123" t="inlineStr">
         <is>
           <t>Garnish for Korean wings</t>
@@ -3872,6 +4115,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G124" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H124" t="inlineStr">
         <is>
           <t>Thai pandan chicken marinade</t>
@@ -3899,6 +4145,9 @@
           <t>Spice rack</t>
         </is>
       </c>
+      <c r="G125" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H125" t="inlineStr">
         <is>
           <t>Beef stew</t>
@@ -3926,6 +4175,9 @@
           <t>Spice rack</t>
         </is>
       </c>
+      <c r="G126" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
           <t>Beef stew</t>
@@ -3953,6 +4205,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G127" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H127" t="inlineStr">
         <is>
           <t>Steamed egg tofu, soups</t>
@@ -3980,6 +4235,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G128" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H128" t="inlineStr">
         <is>
           <t>Sambal kangkong, sambal</t>
@@ -4007,6 +4265,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G129" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H129" t="inlineStr">
         <is>
           <t>Nasi lemak side</t>
@@ -4034,6 +4295,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G130" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H130" t="inlineStr">
         <is>
           <t>Sambal kangkong, sambal</t>
@@ -4061,6 +4325,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G131" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H131" t="inlineStr">
         <is>
           <t>Lotus root soup, nasi lemak</t>
@@ -4088,6 +4355,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G132" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H132" t="inlineStr">
         <is>
           <t>Beef stew</t>
@@ -4115,6 +4385,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G133" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H133" t="inlineStr">
         <is>
           <t>Beef stew braising liquid</t>
@@ -4142,6 +4415,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G134" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
           <t>Pandan chicken, sambal</t>
@@ -4159,15 +4435,18 @@
           <t>Specialty / Asian</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Out</t>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>In stock</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>Pantry</t>
         </is>
+      </c>
+      <c r="G135" s="10" t="n">
+        <v>46277</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -4196,6 +4475,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G136" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
           <t>Japanese mushroom rice</t>
@@ -4223,6 +4505,9 @@
           <t>Spice rack</t>
         </is>
       </c>
+      <c r="G137" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
           <t>Japanese mushroom rice finishing</t>
@@ -4250,6 +4535,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G138" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
           <t>Fishball minced pork soup</t>
@@ -4277,6 +4565,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G139" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
           <t>Ban mian / mee hoon kway broth</t>
@@ -4304,6 +4595,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G140" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H140" t="inlineStr">
         <is>
           <t>Ban mian / mee hoon kway broth</t>
@@ -4331,6 +4625,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G141" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H141" t="inlineStr">
         <is>
           <t>Sticky pork belly braise</t>
@@ -4358,6 +4655,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G142" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H142" t="inlineStr">
         <is>
           <t>Yang Zhou fried rice</t>
@@ -4385,6 +4685,9 @@
           <t>Pantry</t>
         </is>
       </c>
+      <c r="G143" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
           <t>Claypot tofu</t>
@@ -4412,6 +4715,9 @@
           <t>Freezer</t>
         </is>
       </c>
+      <c r="G144" s="10" t="n">
+        <v>46271</v>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
           <t>Cheesy baked rice</t>
@@ -4439,8 +4745,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G145" s="7" t="n">
-        <v>46179</v>
+      <c r="G145" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -4469,8 +4775,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G146" s="7" t="n">
-        <v>46179</v>
+      <c r="G146" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -4499,8 +4805,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G147" s="7" t="n">
-        <v>46179</v>
+      <c r="G147" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -4529,8 +4835,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G148" s="7" t="n">
-        <v>46179</v>
+      <c r="G148" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
@@ -4559,8 +4865,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G149" s="7" t="n">
-        <v>46179</v>
+      <c r="G149" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -4579,9 +4885,9 @@
           <t>Specialty / Asian</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Out</t>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>In stock</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4589,8 +4895,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G150" s="7" t="n">
-        <v>46181</v>
+      <c r="G150" s="10" t="n">
+        <v>46277</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -4619,8 +4925,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G151" s="7" t="n">
-        <v>46181</v>
+      <c r="G151" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -4649,8 +4955,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G152" s="7" t="n">
-        <v>46181</v>
+      <c r="G152" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
@@ -4679,8 +4985,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G153" s="7" t="n">
-        <v>46181</v>
+      <c r="G153" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H153" t="inlineStr">
         <is>
@@ -4709,8 +5015,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G154" s="7" t="n">
-        <v>46181</v>
+      <c r="G154" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H154" t="inlineStr">
         <is>
@@ -4739,8 +5045,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G155" s="7" t="n">
-        <v>46181</v>
+      <c r="G155" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
@@ -4769,8 +5075,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G156" s="7" t="n">
-        <v>46181</v>
+      <c r="G156" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
@@ -4799,8 +5105,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n">
-        <v>46181</v>
+      <c r="G157" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
@@ -4829,8 +5135,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G158" s="7" t="n">
-        <v>46181</v>
+      <c r="G158" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H158" t="inlineStr">
         <is>
@@ -4859,8 +5165,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G159" s="7" t="n">
-        <v>46181</v>
+      <c r="G159" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H159" t="inlineStr">
         <is>
@@ -4889,8 +5195,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G160" s="7" t="n">
-        <v>46181</v>
+      <c r="G160" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
@@ -4919,8 +5225,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G161" s="7" t="n">
-        <v>46181</v>
+      <c r="G161" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
@@ -4949,8 +5255,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G162" s="7" t="n">
-        <v>46181</v>
+      <c r="G162" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
@@ -4979,8 +5285,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G163" s="7" t="n">
-        <v>46181</v>
+      <c r="G163" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
@@ -5009,8 +5315,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G164" s="7" t="n">
-        <v>46181</v>
+      <c r="G164" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
@@ -5039,8 +5345,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G165" s="7" t="n">
-        <v>46181</v>
+      <c r="G165" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
@@ -5069,8 +5375,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G166" s="7" t="n">
-        <v>46181</v>
+      <c r="G166" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
@@ -5099,8 +5405,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G167" s="7" t="n">
-        <v>46181</v>
+      <c r="G167" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
@@ -5129,8 +5435,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G168" s="7" t="n">
-        <v>46181</v>
+      <c r="G168" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
@@ -5159,8 +5465,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G169" s="7" t="n">
-        <v>46181</v>
+      <c r="G169" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
@@ -5189,8 +5495,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G170" s="7" t="n">
-        <v>46181</v>
+      <c r="G170" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
@@ -5219,8 +5525,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G171" s="7" t="n">
-        <v>46181</v>
+      <c r="G171" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
@@ -5249,8 +5555,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G172" s="7" t="n">
-        <v>46181</v>
+      <c r="G172" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
@@ -5279,8 +5585,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G173" s="7" t="n">
-        <v>46181</v>
+      <c r="G173" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
@@ -5309,8 +5615,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G174" s="7" t="n">
-        <v>46181</v>
+      <c r="G174" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H174" t="inlineStr">
         <is>
@@ -5339,8 +5645,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G175" s="7" t="n">
-        <v>46181</v>
+      <c r="G175" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -5369,8 +5675,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G176" s="7" t="n">
-        <v>46181</v>
+      <c r="G176" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H176" t="inlineStr">
         <is>
@@ -5399,8 +5705,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G177" s="7" t="n">
-        <v>46181</v>
+      <c r="G177" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H177" t="inlineStr">
         <is>
@@ -5429,8 +5735,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G178" s="7" t="n">
-        <v>46181</v>
+      <c r="G178" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H178" t="inlineStr">
         <is>
@@ -5459,8 +5765,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G179" s="7" t="n">
-        <v>46181</v>
+      <c r="G179" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
@@ -5489,8 +5795,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G180" s="7" t="n">
-        <v>46181</v>
+      <c r="G180" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -5519,8 +5825,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G181" s="7" t="n">
-        <v>46181</v>
+      <c r="G181" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
@@ -5549,8 +5855,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G182" s="7" t="n">
-        <v>46181</v>
+      <c r="G182" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
@@ -5579,8 +5885,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G183" s="7" t="n">
-        <v>46207</v>
+      <c r="G183" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -5609,8 +5915,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G184" s="7" t="n">
-        <v>46207</v>
+      <c r="G184" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H184" t="inlineStr">
         <is>
@@ -5639,8 +5945,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G185" s="7" t="n">
-        <v>46207</v>
+      <c r="G185" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H185" t="inlineStr">
         <is>
@@ -5669,8 +5975,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G186" s="7" t="n">
-        <v>46207</v>
+      <c r="G186" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
@@ -5699,8 +6005,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n">
-        <v>46207</v>
+      <c r="G187" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
@@ -5729,8 +6035,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G188" s="7" t="n">
-        <v>46207</v>
+      <c r="G188" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
@@ -5759,8 +6065,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G189" s="7" t="n">
-        <v>46207</v>
+      <c r="G189" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
@@ -5789,8 +6095,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G190" s="7" t="n">
-        <v>46207</v>
+      <c r="G190" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H190" t="inlineStr">
         <is>
@@ -5819,8 +6125,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G191" s="7" t="n">
-        <v>46207</v>
+      <c r="G191" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
@@ -5849,8 +6155,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G192" s="7" t="n">
-        <v>46207</v>
+      <c r="G192" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
@@ -5879,8 +6185,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G193" s="7" t="n">
-        <v>46207</v>
+      <c r="G193" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H193" t="inlineStr">
         <is>
@@ -5909,8 +6215,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G194" s="7" t="n">
-        <v>46207</v>
+      <c r="G194" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
@@ -5939,8 +6245,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G195" s="7" t="n">
-        <v>46207</v>
+      <c r="G195" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
@@ -5969,8 +6275,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G196" s="7" t="n">
-        <v>46207</v>
+      <c r="G196" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
@@ -5999,8 +6305,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G197" s="7" t="n">
-        <v>46207</v>
+      <c r="G197" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
@@ -6029,8 +6335,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G198" s="7" t="n">
-        <v>46214</v>
+      <c r="G198" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -6062,8 +6368,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G200" s="7" t="n">
-        <v>46214</v>
+      <c r="G200" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
@@ -6092,8 +6398,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G201" s="7" t="n">
-        <v>46214</v>
+      <c r="G201" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
@@ -6122,8 +6428,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G202" s="7" t="n">
-        <v>46214</v>
+      <c r="G202" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
@@ -6152,8 +6458,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G203" s="7" t="n">
-        <v>46214</v>
+      <c r="G203" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H203" t="inlineStr">
         <is>
@@ -6182,8 +6488,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G204" s="7" t="n">
-        <v>46214</v>
+      <c r="G204" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H204" t="inlineStr">
         <is>
@@ -6212,8 +6518,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G205" s="7" t="n">
-        <v>46214</v>
+      <c r="G205" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
@@ -6242,8 +6548,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G206" s="7" t="n">
-        <v>46214</v>
+      <c r="G206" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
@@ -6272,8 +6578,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G207" s="7" t="n">
-        <v>46214</v>
+      <c r="G207" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
@@ -6302,8 +6608,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G208" s="7" t="n">
-        <v>46214</v>
+      <c r="G208" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
@@ -6332,8 +6638,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G209" s="7" t="n">
-        <v>46214</v>
+      <c r="G209" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
@@ -6362,8 +6668,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G210" s="7" t="n">
-        <v>46214</v>
+      <c r="G210" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
@@ -6392,8 +6698,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G211" s="7" t="n">
-        <v>46214</v>
+      <c r="G211" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
@@ -6422,8 +6728,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G212" s="7" t="n">
-        <v>46214</v>
+      <c r="G212" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
@@ -6452,8 +6758,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G213" s="7" t="n">
-        <v>46214</v>
+      <c r="G213" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
@@ -6482,8 +6788,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G214" s="7" t="n">
-        <v>46214</v>
+      <c r="G214" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H214" t="inlineStr">
         <is>
@@ -6502,9 +6808,9 @@
           <t>Produce</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Out</t>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>In stock</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -6512,8 +6818,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G215" s="7" t="n">
-        <v>46214</v>
+      <c r="G215" s="10" t="n">
+        <v>46277</v>
       </c>
       <c r="H215" t="inlineStr">
         <is>
@@ -6542,8 +6848,8 @@
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="G216" s="7" t="n">
-        <v>46228</v>
+      <c r="G216" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H216" t="inlineStr">
         <is>
@@ -6572,8 +6878,8 @@
           <t>Kitchen</t>
         </is>
       </c>
-      <c r="G217" s="7" t="n">
-        <v>46228</v>
+      <c r="G217" s="10" t="n">
+        <v>46271</v>
       </c>
     </row>
     <row r="218">
@@ -6597,8 +6903,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G218" s="7" t="n">
-        <v>46235</v>
+      <c r="G218" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
@@ -6627,8 +6933,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G219" s="7" t="n">
-        <v>46235</v>
+      <c r="G219" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -6657,8 +6963,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G220" s="7" t="n">
-        <v>46235</v>
+      <c r="G220" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H220" t="inlineStr">
         <is>
@@ -6687,8 +6993,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G221" s="7" t="n">
-        <v>46235</v>
+      <c r="G221" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H221" t="inlineStr">
         <is>
@@ -6717,8 +7023,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G222" s="7" t="n">
-        <v>46235</v>
+      <c r="G222" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
@@ -6747,8 +7053,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G223" s="7" t="n">
-        <v>46235</v>
+      <c r="G223" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
@@ -6777,8 +7083,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G224" s="7" t="n">
-        <v>46235</v>
+      <c r="G224" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H224" t="inlineStr">
         <is>
@@ -6807,8 +7113,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G225" s="7" t="n">
-        <v>46235</v>
+      <c r="G225" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H225" t="inlineStr">
         <is>
@@ -6837,8 +7143,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G226" s="7" t="n">
-        <v>46235</v>
+      <c r="G226" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
@@ -6867,8 +7173,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G227" s="7" t="n">
-        <v>46235</v>
+      <c r="G227" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
@@ -6897,8 +7203,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G228" s="7" t="n">
-        <v>46235</v>
+      <c r="G228" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -6927,8 +7233,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G229" s="7" t="n">
-        <v>46235</v>
+      <c r="G229" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H229" t="inlineStr">
         <is>
@@ -6957,8 +7263,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G230" s="7" t="n">
-        <v>46235</v>
+      <c r="G230" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -6987,8 +7293,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G231" s="7" t="n">
-        <v>46235</v>
+      <c r="G231" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -7017,8 +7323,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G232" s="7" t="n">
-        <v>46235</v>
+      <c r="G232" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -7047,8 +7353,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G233" s="7" t="n">
-        <v>46235</v>
+      <c r="G233" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
@@ -7077,8 +7383,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G234" s="7" t="n">
-        <v>46235</v>
+      <c r="G234" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
@@ -7107,8 +7413,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G235" s="7" t="n">
-        <v>46235</v>
+      <c r="G235" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
@@ -7137,8 +7443,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G236" s="7" t="n">
-        <v>46235</v>
+      <c r="G236" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H236" t="inlineStr">
         <is>
@@ -7167,8 +7473,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G237" s="7" t="n">
-        <v>46235</v>
+      <c r="G237" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -7197,8 +7503,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G238" s="7" t="n">
-        <v>46235</v>
+      <c r="G238" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
@@ -7227,8 +7533,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G239" s="7" t="n">
-        <v>46235</v>
+      <c r="G239" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H239" t="inlineStr">
         <is>
@@ -7257,8 +7563,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G240" s="7" t="n">
-        <v>46235</v>
+      <c r="G240" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
@@ -7287,8 +7593,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G241" s="7" t="n">
-        <v>46235</v>
+      <c r="G241" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
@@ -7317,8 +7623,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G242" s="7" t="n">
-        <v>46235</v>
+      <c r="G242" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
@@ -7347,8 +7653,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G243" s="7" t="n">
-        <v>46235</v>
+      <c r="G243" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
@@ -7377,8 +7683,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G244" s="7" t="n">
-        <v>46242</v>
+      <c r="G244" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -7407,8 +7713,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G245" s="7" t="n">
-        <v>46242</v>
+      <c r="G245" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -7437,8 +7743,8 @@
           <t>Pantry</t>
         </is>
       </c>
-      <c r="G246" s="7" t="n">
-        <v>46242</v>
+      <c r="G246" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -7467,8 +7773,8 @@
           <t>Fridge</t>
         </is>
       </c>
-      <c r="G247" s="7" t="n">
-        <v>46242</v>
+      <c r="G247" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -7497,8 +7803,8 @@
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G248" s="7" t="n">
-        <v>46242</v>
+      <c r="G248" s="10" t="n">
+        <v>46271</v>
       </c>
       <c r="H248" t="inlineStr">
         <is>
@@ -7517,22 +7823,592 @@
           <t>Freezer - Proteins</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr">
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G249" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Fri - using up existing stock</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Baby threadfin (ikan kurau)</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E250" s="4" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G250" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H250" s="4" t="inlineStr">
+        <is>
+          <t>Tue - whole, 1.4kg. Steam time is PER FISH, not total weight</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="inlineStr">
+        <is>
+          <t>Dou miao (pea shoots)</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E251" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G251" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H251" s="4" t="inlineStr">
+        <is>
+          <t>Tue - 600g. Wilts to a fifth</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Daikon (white radish)</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E252" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G252" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H252" s="4" t="inlineStr">
+        <is>
+          <t>Fri radish pork rib soup - 750g. NOT chai poh</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="inlineStr">
+        <is>
+          <t>Kai lan (Chinese broccoli)</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E253" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G253" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H253" s="4" t="inlineStr">
+        <is>
+          <t>Fri - 900g. Hardy green for day 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="inlineStr">
+        <is>
+          <t>Fresh dill</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E254" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G254" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H254" s="4" t="inlineStr">
+        <is>
+          <t>Thu baked salmon with herbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="inlineStr">
+        <is>
+          <t>Frozen mixed vegetables (corn/peas/carrots)</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E255" s="4" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G255" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H255" s="4" t="inlineStr">
+        <is>
+          <t>Wed Yang Zhou fried rice - 1 pack</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="inlineStr">
+        <is>
+          <t>Aluminium foil</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E256" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G256" s="10" t="n">
+        <v>46271</v>
+      </c>
+      <c r="H256" s="4" t="inlineStr">
+        <is>
+          <t>Thu salmon tray. Non-food</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Shredded nori 海苔</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
         <is>
           <t>In stock</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr">
+      <c r="E257" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G257" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H257" s="4" t="inlineStr">
+        <is>
+          <t>Mon buta don - 30g</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="inlineStr">
+        <is>
+          <t>Doubanjiang (soy bean paste) 豆瓣酱</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>In stock</t>
+        </is>
+      </c>
+      <c r="E258" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G258" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H258" s="4" t="inlineStr">
+        <is>
+          <t>Tue Taiwanese beef noodle - 3.25 tbsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Beef shank</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E259" s="4" t="inlineStr">
         <is>
           <t>Freezer</t>
         </is>
       </c>
-      <c r="G249" s="7" t="n">
-        <v>46243</v>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Fri - using up existing stock</t>
+      <c r="G259" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H259" s="4" t="inlineStr">
+        <is>
+          <t>Tue - 1.3-1.5kg, cut in large cubes, with tendon</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="inlineStr">
+        <is>
+          <t>White wheat noodles</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E260" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G260" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H260" s="4" t="inlineStr">
+        <is>
+          <t>Tue beef noodle - 650-800g</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>Minced chicken</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E261" s="4" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G261" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H261" s="4" t="inlineStr">
+        <is>
+          <t>Thu braised meatballs - 290g</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="inlineStr">
+        <is>
+          <t>Pomfret, whole</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E262" s="4" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G262" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H262" s="4" t="inlineStr">
+        <is>
+          <t>Thu - 1.4kg, ideally 2 fish</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Baby spinach</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>In stock</t>
+        </is>
+      </c>
+      <c r="E263" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G263" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H263" s="4" t="inlineStr">
+        <is>
+          <t>Wed fishball soup - 300g. Day-three green</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="inlineStr">
+        <is>
+          <t>Capsicum (bell pepper)</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E264" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G264" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H264" s="4" t="inlineStr">
+        <is>
+          <t>Fri sweet and sour pork</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="inlineStr">
+        <is>
+          <t>Fresh pineapple</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E265" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G265" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H265" s="4" t="inlineStr">
+        <is>
+          <t>Fri sweet and sour pork</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E266" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G266" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H266" s="4" t="inlineStr">
+        <is>
+          <t>Tue beef noodle broth - 1, quartered</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="inlineStr">
+        <is>
+          <t>Tomato sauce (ketchup-style)</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E267" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G267" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H267" s="4" t="inlineStr">
+        <is>
+          <t>Fri sweet and sour gravy - 3 tbsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>Fennel seeds</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E268" s="4" t="inlineStr">
+        <is>
+          <t>Spice rack</t>
+        </is>
+      </c>
+      <c r="G268" s="10" t="n">
+        <v>46277</v>
+      </c>
+      <c r="H268" s="4" t="inlineStr">
+        <is>
+          <t>Tue beef noodle spice bag - 1.5 tsp</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -523,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H268"/>
+  <dimension ref="A1:H282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1490,9 +1491,13 @@
       </c>
       <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="9" t="n">
-        <v>46271</v>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
+        <v>46291</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Mia's pantry report 26 Sep</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3110,9 +3115,13 @@
       </c>
       <c r="F89" s="2" t="inlineStr"/>
       <c r="G89" s="9" t="n">
-        <v>46271</v>
-      </c>
-      <c r="H89" s="2" t="inlineStr"/>
+        <v>46291</v>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>Mia's pantry report 26 Sep</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -3138,9 +3147,13 @@
       </c>
       <c r="F90" s="2" t="inlineStr"/>
       <c r="G90" s="9" t="n">
-        <v>46271</v>
-      </c>
-      <c r="H90" s="2" t="inlineStr"/>
+        <v>46291</v>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>Mia's pantry report 26 Sep</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4225,9 +4238,9 @@
           <t>Specialty / Asian</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Out</t>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -4236,11 +4249,11 @@
         </is>
       </c>
       <c r="G128" s="10" t="n">
-        <v>46271</v>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>Sambal kangkong, sambal</t>
+        <v>46291</v>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>Mia's pantry report 26 Sep</t>
         </is>
       </c>
     </row>
@@ -4887,7 +4900,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>In stock</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -4896,11 +4909,11 @@
         </is>
       </c>
       <c r="G150" s="10" t="n">
-        <v>46277</v>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Tonjiru</t>
+        <v>46291</v>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>Mia's pantry report 26 Sep</t>
         </is>
       </c>
     </row>
@@ -8409,6 +8422,426 @@
       <c r="H268" s="4" t="inlineStr">
         <is>
           <t>Tue beef noodle spice bag - 1.5 tsp</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="inlineStr">
+        <is>
+          <t>Five spice beancurd skin</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E269" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G269" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H269" s="4" t="inlineStr">
+        <is>
+          <t>Hey zho - 2 big sheets</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>Sole fish powder</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E270" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G270" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H270" s="4" t="inlineStr">
+        <is>
+          <t>Hey zho - 1 tbsp. Not anchovy powder</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="inlineStr">
+        <is>
+          <t>Water chestnuts</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E271" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G271" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H271" s="4" t="inlineStr">
+        <is>
+          <t>Hey zho - 8 pieces</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Oxtail</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E272" s="4" t="inlineStr">
+        <is>
+          <t>Freezer</t>
+        </is>
+      </c>
+      <c r="G272" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H272" s="4" t="inlineStr">
+        <is>
+          <t>Hainanese oxtail stew - 2.6kg; shank as fallback</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="inlineStr">
+        <is>
+          <t>Beef stock</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E273" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G273" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H273" s="4" t="inlineStr">
+        <is>
+          <t>Oxtail stew - 1.3L</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Seabass, whole</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E274" s="4" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G274" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H274" s="4" t="inlineStr">
+        <is>
+          <t>HK steamed seabass - 2 x ~600g</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="inlineStr">
+        <is>
+          <t>Swiss cheese</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - Dairy &amp; Eggs</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E275" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - top</t>
+        </is>
+      </c>
+      <c r="G275" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H275" s="4" t="inlineStr">
+        <is>
+          <t>Cubano</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="inlineStr">
+        <is>
+          <t>Dill pickles</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E276" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G276" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H276" s="4" t="inlineStr">
+        <is>
+          <t>Cubano</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="inlineStr">
+        <is>
+          <t>Bread flour</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E277" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G277" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H277" s="4" t="inlineStr">
+        <is>
+          <t>Cubano bread - 500g</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="inlineStr">
+        <is>
+          <t>Active dry yeast</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E278" s="4" t="inlineStr">
+        <is>
+          <t>Pantry</t>
+        </is>
+      </c>
+      <c r="G278" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H278" s="4" t="inlineStr">
+        <is>
+          <t>Cubano bread</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Boiled ham (sliced)</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E279" s="4" t="inlineStr">
+        <is>
+          <t>Fridge</t>
+        </is>
+      </c>
+      <c r="G279" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H279" s="4" t="inlineStr">
+        <is>
+          <t>Cubano - 20-24 slices, sear before use</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="inlineStr">
+        <is>
+          <t>Fresh mint</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E280" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G280" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H280" s="4" t="inlineStr">
+        <is>
+          <t>Cubano marinade</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Fresh oregano</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E281" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G281" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H281" s="4" t="inlineStr">
+        <is>
+          <t>Cubano marinade</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="inlineStr">
+        <is>
+          <t>Sweet corn (fresh)</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E282" s="4" t="inlineStr">
+        <is>
+          <t>Fridge - crisper</t>
+        </is>
+      </c>
+      <c r="G282" s="11" t="n">
+        <v>46291</v>
+      </c>
+      <c r="H282" s="4" t="inlineStr">
+        <is>
+          <t>ABC soup - 2 cobs</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H282"/>
+  <dimension ref="A1:H295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -8842,6 +8842,344 @@
       <c r="H282" s="4" t="inlineStr">
         <is>
           <t>ABC soup - 2 cobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>Rice flour</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E283" s="4" t="n"/>
+      <c r="G283" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H283" s="4" t="inlineStr">
+        <is>
+          <t>Tue fried chicken wings batter, about 65g. Not glutinous rice flour (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="4" t="inlineStr">
+        <is>
+          <t>MSG</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E284" s="4" t="n"/>
+      <c r="G284" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H284" s="4" t="inlineStr">
+        <is>
+          <t>Tue fried chicken wings batter, about 1¼ tsp (half the recipe's scaled 2½ tsp) (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>Korean sweet potato glass noodles (dangmyeon)</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>Dry Goods</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E285" s="4" t="n"/>
+      <c r="G285" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H285" s="4" t="inlineStr">
+        <is>
+          <t>Sun japchae, 160g. Not tanghoon (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>Red fermented bean curd 南乳</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E286" s="4" t="n"/>
+      <c r="G286" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H286" s="4" t="inlineStr">
+        <is>
+          <t>Mon Hakka yam pork belly, 1 piece + 3/4 tbsp liquid. Recipe doesn't say red or white; red assumed (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="4" t="inlineStr">
+        <is>
+          <t>Chinese white rice wine 米酒</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E287" s="4" t="n"/>
+      <c r="G287" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H287" s="4" t="inlineStr">
+        <is>
+          <t>Mon Hakka yam pork belly marinade, 3/4 tbsp. Not Shaoxing (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="4" t="inlineStr">
+        <is>
+          <t>Sakura prawns (dried)</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E288" s="4" t="n"/>
+      <c r="G288" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H288" s="4" t="inlineStr">
+        <is>
+          <t>Mon Hakka yam pork belly, 4g, optional. Not the same as dried shrimp (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="4" t="inlineStr">
+        <is>
+          <t>Japanese soy sauce (premium light, e.g. Kikkoman)</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E289" s="4" t="n"/>
+      <c r="G289" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H289" s="4" t="inlineStr">
+        <is>
+          <t>Wed Japanese curry, about 3 tbsp (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>Minced lamb</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E290" s="4" t="n"/>
+      <c r="G290" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H290" s="4" t="inlineStr">
+        <is>
+          <t>Fri shepherd's pie, about 1kg. Minced beef works too (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="4" t="inlineStr">
+        <is>
+          <t>Fresh rosemary</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E291" s="4" t="n"/>
+      <c r="G291" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H291" s="4" t="inlineStr">
+        <is>
+          <t>Fri shepherd's pie, small bunch, cooked into the filling (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>Swiss brown / cremini mushrooms (fresh)</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E292" s="4" t="n"/>
+      <c r="G292" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H292" s="4" t="inlineStr">
+        <is>
+          <t>Fri mushroom soup, about 625g (3 boxes). Day 5 off the shop, so keep them in a paper bag (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="4" t="inlineStr">
+        <is>
+          <t>Beef stock cubes (bouillon)</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E293" s="4" t="n"/>
+      <c r="G293" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H293" s="4" t="inlineStr">
+        <is>
+          <t>Fri mushroom soup, 2 cubes. Separate from the existing liquid 'Beef stock' (Canned/Jarred) row (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>Dry white wine / Marsala (cooking)</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E294" s="4" t="n"/>
+      <c r="G294" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H294" s="4" t="inlineStr">
+        <is>
+          <t>Fri mushroom soup, about 110ml. Any dry white or red also works (the existing 'Red wine (cooking)' row covers red) (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="4" t="inlineStr">
+        <is>
+          <t>Choy sum / xiao bai cai</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E295" s="4" t="n"/>
+      <c r="G295" s="11" t="n">
+        <v>46299</v>
+      </c>
+      <c r="H295" s="4" t="inlineStr">
+        <is>
+          <t>Tue stir fried vegetable, about 700g (estimate). Day 2 off the shop (added week of 5 Oct 2026)</t>
         </is>
       </c>
     </row>

--- a/kitchen-inventory.xlsx
+++ b/kitchen-inventory.xlsx
@@ -524,7 +524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H295"/>
+  <dimension ref="A1:H314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9180,6 +9180,500 @@
       <c r="H295" s="4" t="inlineStr">
         <is>
           <t>Tue stir fried vegetable, about 700g (estimate). Day 2 off the shop (added week of 5 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>Chuno sauce (Japanese)</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E296" s="4" t="n"/>
+      <c r="G296" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H296" s="4" t="inlineStr">
+        <is>
+          <t>Sun hayashi rice, 2 tbsp (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="4" t="inlineStr">
+        <is>
+          <t>Porcini powder</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E297" s="4" t="n"/>
+      <c r="G297" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H297" s="4" t="inlineStr">
+        <is>
+          <t>Sun hayashi rice, 2 tsp (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="4" t="inlineStr">
+        <is>
+          <t>Dijon mustard</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Sauces &amp; Condiments</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E298" s="4" t="n"/>
+      <c r="G298" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H298" s="4" t="inlineStr">
+        <is>
+          <t>Mon Greek lemon chicken, 2 tsp (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="4" t="inlineStr">
+        <is>
+          <t>Dried oregano</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E299" s="4" t="n"/>
+      <c r="G299" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H299" s="4" t="inlineStr">
+        <is>
+          <t>Mon Greek lemon chicken, 1 tbsp. Separate from the Fresh oregano row (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="4" t="inlineStr">
+        <is>
+          <t>Dried thyme</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Spices &amp; Seasonings</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E300" s="4" t="n"/>
+      <c r="G300" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H300" s="4" t="inlineStr">
+        <is>
+          <t>Mon Greek lemon chicken, 2 tsp. Separate from the Fresh thyme row (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>Fresh basil</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E301" s="4" t="n"/>
+      <c r="G301" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H301" s="4" t="inlineStr">
+        <is>
+          <t>Mon roasted vegetables, a handful folded in hot. Optional (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="4" t="inlineStr">
+        <is>
+          <t>Zucchini</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E302" s="4" t="n"/>
+      <c r="G302" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H302" s="4" t="inlineStr">
+        <is>
+          <t>Mon roasted vegetables, 1 large (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>Cauliflower</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E303" s="4" t="n"/>
+      <c r="G303" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H303" s="4" t="inlineStr">
+        <is>
+          <t>Mon roasted vegetables, 1 small head (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="inlineStr">
+        <is>
+          <t>French beans</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E304" s="4" t="n"/>
+      <c r="G304" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H304" s="4" t="inlineStr">
+        <is>
+          <t>Thu stir fried French beans, 500g (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>Enoki mushrooms</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E305" s="4" t="n"/>
+      <c r="G305" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H305" s="4" t="inlineStr">
+        <is>
+          <t>Sun hayashi rice, 200g (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="inlineStr">
+        <is>
+          <t>Chicken thighs (bone-in)</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E306" s="4" t="n"/>
+      <c r="G306" s="11" t="n">
+        <v>46304</v>
+      </c>
+      <c r="H306" s="4" t="inlineStr">
+        <is>
+          <t>Mon Greek lemon chicken, 5 thighs (at home; recipe is for 8, marinade x0.6) (added week of 12 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>Dancing Chef Thai green curry paste</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E307" s="4" t="n"/>
+      <c r="G307" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H307" s="4" t="inlineStr">
+        <is>
+          <t>Sun green curry, 1 packet; follow the packet (added week of 19 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="inlineStr">
+        <is>
+          <t>Eggplant</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E308" s="4" t="n"/>
+      <c r="G308" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H308" s="4" t="inlineStr">
+        <is>
+          <t>Sun green curry, 1 (added week of 19 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="inlineStr">
+        <is>
+          <t>Leek (large)</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E309" s="4" t="n"/>
+      <c r="G309" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H309" s="4" t="inlineStr">
+        <is>
+          <t>Thu pan-fried threadfin, 1 large. Separate from the Japanese leek row (added week of 19 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="inlineStr">
+        <is>
+          <t>Pork shabu-shabu slices</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>Freezer - Proteins</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E310" s="4" t="n"/>
+      <c r="G310" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H310" s="4" t="inlineStr">
+        <is>
+          <t>Thu enoki with pork wrap, 500g (added week of 19 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="inlineStr">
+        <is>
+          <t>Kara coconut milk (65ml / 200ml packs)</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>Canned/Jarred</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E311" s="4" t="n"/>
+      <c r="G311" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H311" s="4" t="inlineStr">
+        <is>
+          <t>Sun green curry, 200ml. The household buys Kara packs, not cans (added week of 19 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>Baking paper</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Household / Cleaning</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E312" s="4" t="n"/>
+      <c r="G312" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H312" s="4" t="inlineStr">
+        <is>
+          <t>Wed baked chicken wings (added week of 19 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="inlineStr">
+        <is>
+          <t>Sambal belacan paste (instant)</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Specialty / Asian</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E313" s="4" t="n"/>
+      <c r="G313" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H313" s="4" t="inlineStr">
+        <is>
+          <t>Tue si ji dou dried shrimp sambal, 2 heaped tbsp (added week of 19 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>Wawa vegetable (baby napa cabbage)</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>Produce</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="E314" s="4" t="n"/>
+      <c r="G314" s="11" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H314" s="4" t="inlineStr">
+        <is>
+          <t>Wed fishball soup, 1 pack (added week of 19 Oct 2026)</t>
         </is>
       </c>
     </row>
